--- a/Greyform/Python_Application/PBU_TERRAHL2(final).xlsx
+++ b/Greyform/Python_Application/PBU_TERRAHL2(final).xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N13"/>
+  <dimension ref="A1:N43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,7 +549,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Basic Wall:BSS.50:1090838</t>
+          <t>Floor:BSS.115:1090847</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -561,8 +561,10 @@
       <c r="E3" t="n">
         <v>-322</v>
       </c>
-      <c r="F3" t="n">
-        <v>2</v>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="G3" t="n">
         <v>6</v>
@@ -573,10 +575,10 @@
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="n">
-        <v>1200</v>
+        <v>2760</v>
       </c>
       <c r="L3" t="n">
-        <v>2595</v>
+        <v>1800</v>
       </c>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
@@ -589,7 +591,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Basic Wall:BSS.50:1090837</t>
+          <t>Floor:BSS.20mm Floor Finishes (600x600mm):1090854</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -601,8 +603,10 @@
       <c r="E4" t="n">
         <v>-185</v>
       </c>
-      <c r="F4" t="n">
-        <v>3</v>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="G4" t="n">
         <v>6</v>
@@ -613,10 +617,10 @@
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="n">
-        <v>960</v>
+        <v>2760</v>
       </c>
       <c r="L4" t="n">
-        <v>2595</v>
+        <v>1800</v>
       </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
@@ -629,7 +633,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Basic Wall:BSS.50:1090836</t>
+          <t>Floor:BSS.20mm Floor Finishes (600x150mm):1090859</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -641,8 +645,10 @@
       <c r="E5" t="n">
         <v>-1185</v>
       </c>
-      <c r="F5" t="n">
-        <v>4</v>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="G5" t="n">
         <v>6</v>
@@ -653,10 +659,10 @@
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="n">
-        <v>600</v>
+        <v>2760</v>
       </c>
       <c r="L5" t="n">
-        <v>2595</v>
+        <v>1800</v>
       </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
@@ -669,7 +675,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Basic Wall:BSS.50:1090835</t>
+          <t>Floor:BSS.90:1090864</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -681,8 +687,10 @@
       <c r="E6" t="n">
         <v>252</v>
       </c>
-      <c r="F6" t="n">
-        <v>5</v>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="G6" t="n">
         <v>6</v>
@@ -693,10 +701,10 @@
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="n">
-        <v>1800</v>
+        <v>2760</v>
       </c>
       <c r="L6" t="n">
-        <v>2595</v>
+        <v>1800</v>
       </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
@@ -709,7 +717,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Basic Wall:BSS.50:1090834</t>
+          <t>Floor:BSS.80:1090926</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -721,8 +729,10 @@
       <c r="E7" t="n">
         <v>-535</v>
       </c>
-      <c r="F7" t="n">
-        <v>6</v>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="G7" t="n">
         <v>6</v>
@@ -733,10 +743,10 @@
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="n">
-        <v>1800</v>
+        <v>2760</v>
       </c>
       <c r="L7" t="n">
-        <v>2595</v>
+        <v>1800</v>
       </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
@@ -749,7 +759,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Floor:BSS.115:1090847</t>
+          <t>Floor:BSS.20mm Floor Finishes (600x150mm):1091107</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -791,7 +801,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Floor:BSS.20mm Floor Finishes (600x600mm):1090854</t>
+          <t>Basic Wall:BSS.50:1090838</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -803,10 +813,8 @@
       <c r="E9" t="n">
         <v>1240</v>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
+      <c r="F9" t="n">
+        <v>2</v>
       </c>
       <c r="G9" t="n">
         <v>6</v>
@@ -817,10 +825,10 @@
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="n">
-        <v>2760</v>
+        <v>1200</v>
       </c>
       <c r="L9" t="n">
-        <v>1800</v>
+        <v>2595</v>
       </c>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
@@ -833,7 +841,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Floor:BSS.20mm Floor Finishes (600x150mm):1090859</t>
+          <t>Floor:BSS.115:1090847</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -875,7 +883,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Floor:BSS.90:1090864</t>
+          <t>Floor:BSS.20mm Floor Finishes (600x600mm):1090854</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -917,7 +925,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Floor:BSS.80:1090926</t>
+          <t>Floor:BSS.20mm Floor Finishes (600x150mm):1090859</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -959,7 +967,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Floor:BSS.20mm Floor Finishes (600x150mm):1091107</t>
+          <t>Floor:BSS.90:1090864</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -992,6 +1000,1084 @@
       </c>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Tile</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Floor:BSS.80:1090926</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>-550</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1870</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-35</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>6</v>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="n">
+        <v>2760</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1800</v>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Tile</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Floor:BSS.20mm Floor Finishes (600x150mm):1091107</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>6</v>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="n">
+        <v>2760</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1800</v>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Tile</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Basic Wall:BSS.50:1090837</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="n">
+        <v>3</v>
+      </c>
+      <c r="G16" t="n">
+        <v>6</v>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="n">
+        <v>1</v>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="n">
+        <v>960</v>
+      </c>
+      <c r="L16" t="n">
+        <v>2595</v>
+      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Tile</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Floor:BSS.115:1090847</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>6</v>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="n">
+        <v>2760</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1800</v>
+      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Tile</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Floor:BSS.20mm Floor Finishes (600x600mm):1090854</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>6</v>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="n">
+        <v>2760</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1800</v>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Tile</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Floor:BSS.20mm Floor Finishes (600x150mm):1090859</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>6</v>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="n">
+        <v>2760</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1800</v>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Tile</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Floor:BSS.90:1090864</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>6</v>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="n">
+        <v>1</v>
+      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="n">
+        <v>2760</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1800</v>
+      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Tile</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Floor:BSS.80:1090926</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>6</v>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="n">
+        <v>2760</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1800</v>
+      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Tile</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Floor:BSS.20mm Floor Finishes (600x150mm):1091107</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>6</v>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="n">
+        <v>1</v>
+      </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="n">
+        <v>2760</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1800</v>
+      </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Tile</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Basic Wall:BSS.50:1090836</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="n">
+        <v>4</v>
+      </c>
+      <c r="G23" t="n">
+        <v>6</v>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="n">
+        <v>1</v>
+      </c>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="n">
+        <v>600</v>
+      </c>
+      <c r="L23" t="n">
+        <v>2595</v>
+      </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Tile</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Floor:BSS.115:1090847</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>6</v>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="n">
+        <v>1</v>
+      </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="n">
+        <v>2760</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1800</v>
+      </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Tile</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Floor:BSS.20mm Floor Finishes (600x600mm):1090854</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>6</v>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="n">
+        <v>1</v>
+      </c>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="n">
+        <v>2760</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1800</v>
+      </c>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Tile</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Floor:BSS.20mm Floor Finishes (600x150mm):1090859</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>6</v>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="n">
+        <v>1</v>
+      </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="n">
+        <v>2760</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1800</v>
+      </c>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Tile</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Floor:BSS.90:1090864</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>6</v>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="n">
+        <v>1</v>
+      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="n">
+        <v>2760</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1800</v>
+      </c>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Tile</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Floor:BSS.80:1090926</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>6</v>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="n">
+        <v>1</v>
+      </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="n">
+        <v>2760</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1800</v>
+      </c>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Tile</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Floor:BSS.20mm Floor Finishes (600x150mm):1091107</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>6</v>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="n">
+        <v>1</v>
+      </c>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="n">
+        <v>2760</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1800</v>
+      </c>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Tile</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Basic Wall:BSS.50:1090835</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="n">
+        <v>5</v>
+      </c>
+      <c r="G30" t="n">
+        <v>6</v>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="n">
+        <v>1</v>
+      </c>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="n">
+        <v>1800</v>
+      </c>
+      <c r="L30" t="n">
+        <v>2595</v>
+      </c>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Tile</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Floor:BSS.115:1090847</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>6</v>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="n">
+        <v>1</v>
+      </c>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="n">
+        <v>2760</v>
+      </c>
+      <c r="L31" t="n">
+        <v>1800</v>
+      </c>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Tile</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Floor:BSS.20mm Floor Finishes (600x600mm):1090854</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>6</v>
+      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="n">
+        <v>1</v>
+      </c>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="n">
+        <v>2760</v>
+      </c>
+      <c r="L32" t="n">
+        <v>1800</v>
+      </c>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Tile</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Floor:BSS.20mm Floor Finishes (600x150mm):1090859</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>6</v>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="n">
+        <v>1</v>
+      </c>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="n">
+        <v>2760</v>
+      </c>
+      <c r="L33" t="n">
+        <v>1800</v>
+      </c>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Tile</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Floor:BSS.90:1090864</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>6</v>
+      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="n">
+        <v>1</v>
+      </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="n">
+        <v>2760</v>
+      </c>
+      <c r="L34" t="n">
+        <v>1800</v>
+      </c>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Tile</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Floor:BSS.80:1090926</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>6</v>
+      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="n">
+        <v>1</v>
+      </c>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="n">
+        <v>2760</v>
+      </c>
+      <c r="L35" t="n">
+        <v>1800</v>
+      </c>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Tile</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Floor:BSS.20mm Floor Finishes (600x150mm):1091107</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>6</v>
+      </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="n">
+        <v>1</v>
+      </c>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="n">
+        <v>2760</v>
+      </c>
+      <c r="L36" t="n">
+        <v>1800</v>
+      </c>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Tile</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Basic Wall:BSS.50:1090834</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="n">
+        <v>6</v>
+      </c>
+      <c r="G37" t="n">
+        <v>6</v>
+      </c>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="n">
+        <v>1</v>
+      </c>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="n">
+        <v>1800</v>
+      </c>
+      <c r="L37" t="n">
+        <v>2595</v>
+      </c>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Tile</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Floor:BSS.115:1090847</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>6</v>
+      </c>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="n">
+        <v>1</v>
+      </c>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="n">
+        <v>2760</v>
+      </c>
+      <c r="L38" t="n">
+        <v>1800</v>
+      </c>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Tile</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Floor:BSS.20mm Floor Finishes (600x600mm):1090854</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>6</v>
+      </c>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="n">
+        <v>1</v>
+      </c>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="n">
+        <v>2760</v>
+      </c>
+      <c r="L39" t="n">
+        <v>1800</v>
+      </c>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Tile</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Floor:BSS.20mm Floor Finishes (600x150mm):1090859</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>6</v>
+      </c>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="n">
+        <v>1</v>
+      </c>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="n">
+        <v>2760</v>
+      </c>
+      <c r="L40" t="n">
+        <v>1800</v>
+      </c>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Tile</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Floor:BSS.90:1090864</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>6</v>
+      </c>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="n">
+        <v>1</v>
+      </c>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="n">
+        <v>2760</v>
+      </c>
+      <c r="L41" t="n">
+        <v>1800</v>
+      </c>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Tile</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Floor:BSS.80:1090926</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>6</v>
+      </c>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="n">
+        <v>1</v>
+      </c>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="n">
+        <v>2760</v>
+      </c>
+      <c r="L42" t="n">
+        <v>1800</v>
+      </c>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Tile</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Floor:BSS.20mm Floor Finishes (600x150mm):1091107</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>6</v>
+      </c>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="n">
+        <v>1</v>
+      </c>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="n">
+        <v>2760</v>
+      </c>
+      <c r="L43" t="n">
+        <v>1800</v>
+      </c>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Greyform/Python_Application/PBU_TERRAHL2(final).xlsx
+++ b/Greyform/Python_Application/PBU_TERRAHL2(final).xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J74"/>
+  <dimension ref="A1:J59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,17 +462,17 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>Width</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Height</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Status</t>
         </is>
       </c>
     </row>
@@ -485,12 +485,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>TMP1S2a1</t>
+          <t>TileMarkingPoint1S2a1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>Tiles Point</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -500,18 +500,18 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>-750</v>
-      </c>
-      <c r="H2" t="n">
-        <v>2900</v>
+        <v>-775</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>blank</t>
+        </is>
       </c>
       <c r="I2" t="n">
-        <v>2595</v>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>blank</t>
-        </is>
+        <v>2900</v>
+      </c>
+      <c r="J2" t="n">
+        <v>2595</v>
       </c>
     </row>
     <row r="3">
@@ -523,12 +523,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>TMP1S2a2</t>
+          <t>TileMarkingPoint1S2a2</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>Tiles Point</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -538,18 +538,18 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>-150</v>
-      </c>
-      <c r="H3" t="n">
-        <v>2900</v>
+        <v>-175</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>blank</t>
+        </is>
       </c>
       <c r="I3" t="n">
-        <v>2595</v>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>blank</t>
-        </is>
+        <v>2900</v>
+      </c>
+      <c r="J3" t="n">
+        <v>2595</v>
       </c>
     </row>
     <row r="4">
@@ -561,12 +561,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>TMP1S2a3</t>
+          <t>TileMarkingPoint1S2a3</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>Tiles Point</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -576,18 +576,18 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>450</v>
-      </c>
-      <c r="H4" t="n">
-        <v>2900</v>
+        <v>425</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>blank</t>
+        </is>
       </c>
       <c r="I4" t="n">
-        <v>2595</v>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>blank</t>
-        </is>
+        <v>2900</v>
+      </c>
+      <c r="J4" t="n">
+        <v>2595</v>
       </c>
     </row>
     <row r="5">
@@ -599,12 +599,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>TMP1S2a4</t>
+          <t>TileMarkingPoint1S2a4</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>Tiles Point</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -614,18 +614,18 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>1050</v>
-      </c>
-      <c r="H5" t="n">
-        <v>2900</v>
+        <v>1025</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>blank</t>
+        </is>
       </c>
       <c r="I5" t="n">
-        <v>2595</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>blank</t>
-        </is>
+        <v>2900</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2595</v>
       </c>
     </row>
     <row r="6">
@@ -637,12 +637,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>TMP1S2b1</t>
+          <t>TileMarkingPoint1S2b1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>Tiles Point</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -652,18 +652,18 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>-750</v>
-      </c>
-      <c r="H6" t="n">
-        <v>2900</v>
+        <v>-775</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>blank</t>
+        </is>
       </c>
       <c r="I6" t="n">
-        <v>2595</v>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>blank</t>
-        </is>
+        <v>2900</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2595</v>
       </c>
     </row>
     <row r="7">
@@ -675,12 +675,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>TMP1S2b2</t>
+          <t>TileMarkingPoint1S2b2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>Tiles Point</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -690,18 +690,18 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>-150</v>
-      </c>
-      <c r="H7" t="n">
-        <v>2900</v>
+        <v>-175</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>blank</t>
+        </is>
       </c>
       <c r="I7" t="n">
-        <v>2595</v>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>blank</t>
-        </is>
+        <v>2900</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2595</v>
       </c>
     </row>
     <row r="8">
@@ -713,12 +713,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>TMP1S2b3</t>
+          <t>TileMarkingPoint1S2b3</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>Tiles Point</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -728,18 +728,18 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>450</v>
-      </c>
-      <c r="H8" t="n">
-        <v>2900</v>
+        <v>425</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>blank</t>
+        </is>
       </c>
       <c r="I8" t="n">
-        <v>2595</v>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>blank</t>
-        </is>
+        <v>2900</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2595</v>
       </c>
     </row>
     <row r="9">
@@ -751,12 +751,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>TMP1S2b4</t>
+          <t>TileMarkingPoint1S2b4</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>Tiles Point</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -766,18 +766,18 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>1050</v>
-      </c>
-      <c r="H9" t="n">
-        <v>2900</v>
+        <v>1025</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>blank</t>
+        </is>
       </c>
       <c r="I9" t="n">
-        <v>2595</v>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>blank</t>
-        </is>
+        <v>2900</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2595</v>
       </c>
     </row>
     <row r="10">
@@ -789,12 +789,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>TMP1S2c1</t>
+          <t>TileMarkingPoint1S2c1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>Tiles Point</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -804,18 +804,18 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>-750</v>
-      </c>
-      <c r="H10" t="n">
-        <v>2900</v>
+        <v>-775</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>blank</t>
+        </is>
       </c>
       <c r="I10" t="n">
-        <v>2595</v>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>blank</t>
-        </is>
+        <v>2900</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2595</v>
       </c>
     </row>
     <row r="11">
@@ -827,12 +827,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>TMP1S2c2</t>
+          <t>TileMarkingPoint1S2c2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>Tiles Point</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -842,18 +842,18 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>-150</v>
-      </c>
-      <c r="H11" t="n">
-        <v>2900</v>
+        <v>-175</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>blank</t>
+        </is>
       </c>
       <c r="I11" t="n">
-        <v>2595</v>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>blank</t>
-        </is>
+        <v>2900</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2595</v>
       </c>
     </row>
     <row r="12">
@@ -865,12 +865,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>TMP1S2c3</t>
+          <t>TileMarkingPoint1S2c3</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>Tiles Point</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -880,18 +880,18 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>450</v>
-      </c>
-      <c r="H12" t="n">
-        <v>2900</v>
+        <v>425</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>blank</t>
+        </is>
       </c>
       <c r="I12" t="n">
-        <v>2595</v>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>blank</t>
-        </is>
+        <v>2900</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2595</v>
       </c>
     </row>
     <row r="13">
@@ -903,12 +903,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>TMP1S2c4</t>
+          <t>TileMarkingPoint1S2c4</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>Tiles Point</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -918,18 +918,18 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>1050</v>
-      </c>
-      <c r="H13" t="n">
-        <v>2900</v>
+        <v>1025</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>blank</t>
+        </is>
       </c>
       <c r="I13" t="n">
-        <v>2595</v>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>blank</t>
-        </is>
+        <v>2900</v>
+      </c>
+      <c r="J13" t="n">
+        <v>2595</v>
       </c>
     </row>
     <row r="14">
@@ -941,12 +941,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>TMP1S2d1</t>
+          <t>TileMarkingPoint1S2d1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>Tiles Point</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -956,18 +956,18 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>-750</v>
-      </c>
-      <c r="H14" t="n">
-        <v>2900</v>
+        <v>-775</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>blank</t>
+        </is>
       </c>
       <c r="I14" t="n">
-        <v>2595</v>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>blank</t>
-        </is>
+        <v>2900</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2595</v>
       </c>
     </row>
     <row r="15">
@@ -979,12 +979,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>TMP1S2d2</t>
+          <t>TileMarkingPoint1S2d2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>Tiles Point</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -994,18 +994,18 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>-150</v>
-      </c>
-      <c r="H15" t="n">
-        <v>2900</v>
+        <v>-175</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>blank</t>
+        </is>
       </c>
       <c r="I15" t="n">
-        <v>2595</v>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>blank</t>
-        </is>
+        <v>2900</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2595</v>
       </c>
     </row>
     <row r="16">
@@ -1017,12 +1017,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>TMP1S2d3</t>
+          <t>TileMarkingPoint1S2d3</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>Tiles Point</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -1032,18 +1032,18 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>450</v>
-      </c>
-      <c r="H16" t="n">
-        <v>2900</v>
+        <v>425</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>blank</t>
+        </is>
       </c>
       <c r="I16" t="n">
-        <v>2595</v>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>blank</t>
-        </is>
+        <v>2900</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2595</v>
       </c>
     </row>
     <row r="17">
@@ -1055,12 +1055,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>TMP1S2d4</t>
+          <t>TileMarkingPoint1S2d4</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>Tiles Point</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -1070,1391 +1070,1419 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>1050</v>
-      </c>
-      <c r="H17" t="n">
-        <v>2900</v>
+        <v>1025</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>blank</t>
+        </is>
       </c>
       <c r="I17" t="n">
-        <v>2595</v>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>blank</t>
-        </is>
+        <v>2900</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2595</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>TMP1S2e1</t>
+          <t>TileMarkingPoint2S2a1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>Tiles Point</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>796</v>
       </c>
       <c r="G18" t="n">
-        <v>-750</v>
-      </c>
-      <c r="H18" t="n">
-        <v>2900</v>
+        <v>-775</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>blank</t>
+        </is>
       </c>
       <c r="I18" t="n">
-        <v>2595</v>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>blank</t>
-        </is>
+        <v>1340</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2595</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>TMP1S2e2</t>
+          <t>TileMarkingPoint2S2a2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>Tiles Point</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>796</v>
       </c>
       <c r="G19" t="n">
-        <v>-150</v>
-      </c>
-      <c r="H19" t="n">
-        <v>2900</v>
+        <v>-175</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>blank</t>
+        </is>
       </c>
       <c r="I19" t="n">
-        <v>2595</v>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>blank</t>
-        </is>
+        <v>1340</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2595</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>TMP1S2e3</t>
+          <t>TileMarkingPoint2S2b1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>Tiles Point</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>196</v>
       </c>
       <c r="G20" t="n">
-        <v>450</v>
-      </c>
-      <c r="H20" t="n">
-        <v>2900</v>
+        <v>-775</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>blank</t>
+        </is>
       </c>
       <c r="I20" t="n">
-        <v>2595</v>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>blank</t>
-        </is>
+        <v>1340</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2595</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>TMP1S2e4</t>
+          <t>TileMarkingPoint2S2b2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>Tiles Point</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>196</v>
       </c>
       <c r="G21" t="n">
-        <v>1050</v>
-      </c>
-      <c r="H21" t="n">
-        <v>2900</v>
+        <v>-175</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>blank</t>
+        </is>
       </c>
       <c r="I21" t="n">
-        <v>2595</v>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>blank</t>
-        </is>
+        <v>1340</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2595</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>TMP1S2f1</t>
+          <t>TileMarkingPoint3S2a1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>Tiles Point</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1350</v>
+        <v>935</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>-750</v>
-      </c>
-      <c r="H22" t="n">
-        <v>2900</v>
+        <v>-775</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>blank</t>
+        </is>
       </c>
       <c r="I22" t="n">
-        <v>2595</v>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>blank</t>
-        </is>
+        <v>960</v>
+      </c>
+      <c r="J22" t="n">
+        <v>2595</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>TMP1S2f2</t>
+          <t>TileMarkingPoint3S2a2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>Tiles Point</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1350</v>
+        <v>935</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>-150</v>
-      </c>
-      <c r="H23" t="n">
-        <v>2900</v>
+        <v>-175</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>blank</t>
+        </is>
       </c>
       <c r="I23" t="n">
-        <v>2595</v>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>blank</t>
-        </is>
+        <v>960</v>
+      </c>
+      <c r="J23" t="n">
+        <v>2595</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B24" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>TMP1S2f3</t>
+          <t>TileMarkingPoint3S2a3</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>Tiles Point</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1350</v>
+        <v>935</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>450</v>
-      </c>
-      <c r="H24" t="n">
-        <v>2900</v>
+        <v>425</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>blank</t>
+        </is>
       </c>
       <c r="I24" t="n">
-        <v>2595</v>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>blank</t>
-        </is>
+        <v>960</v>
+      </c>
+      <c r="J24" t="n">
+        <v>2595</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>TMP1S2f4</t>
+          <t>TileMarkingPoint3S2a4</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>Tiles Point</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1350</v>
+        <v>935</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>1050</v>
-      </c>
-      <c r="H25" t="n">
-        <v>2900</v>
+        <v>1025</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>blank</t>
+        </is>
       </c>
       <c r="I25" t="n">
-        <v>2595</v>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>blank</t>
-        </is>
+        <v>960</v>
+      </c>
+      <c r="J25" t="n">
+        <v>2595</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="B26" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>CP1S2</t>
+          <t>TileMarkingPoint4S2a1</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Tiles Point</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1450</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>-304</v>
       </c>
       <c r="G26" t="n">
-        <v>975</v>
-      </c>
-      <c r="H26" t="n">
-        <v>2900</v>
+        <v>-175</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>blank</t>
+        </is>
       </c>
       <c r="I26" t="n">
-        <v>2595</v>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>blank</t>
-        </is>
+        <v>592</v>
+      </c>
+      <c r="J26" t="n">
+        <v>2595</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="B27" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>TMP2S2a1</t>
+          <t>TileMarkingPoint4S2a2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>Tiles Point</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>796</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>100</v>
+        <v>-304</v>
       </c>
       <c r="G27" t="n">
-        <v>-750</v>
-      </c>
-      <c r="H27" t="n">
-        <v>1340</v>
+        <v>425</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>blank</t>
+        </is>
       </c>
       <c r="I27" t="n">
-        <v>2595</v>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>blank</t>
-        </is>
+        <v>592</v>
+      </c>
+      <c r="J27" t="n">
+        <v>2595</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="B28" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>TMP2S2a2</t>
+          <t>TileMarkingPoint4S2a3</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>Tiles Point</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>796</v>
+        <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>100</v>
+        <v>-304</v>
       </c>
       <c r="G28" t="n">
-        <v>-150</v>
-      </c>
-      <c r="H28" t="n">
-        <v>1340</v>
+        <v>1025</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>blank</t>
+        </is>
       </c>
       <c r="I28" t="n">
-        <v>2595</v>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>blank</t>
-        </is>
+        <v>592</v>
+      </c>
+      <c r="J28" t="n">
+        <v>2595</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="B29" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>TMP2S2b1</t>
+          <t>TileMarkingPoint5S2a1</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>Tiles Point</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>196</v>
+        <v>-30</v>
       </c>
       <c r="F29" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>-750</v>
-      </c>
-      <c r="H29" t="n">
-        <v>1340</v>
+        <v>-775</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>blank</t>
+        </is>
       </c>
       <c r="I29" t="n">
-        <v>2595</v>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>blank</t>
-        </is>
+        <v>1940</v>
+      </c>
+      <c r="J29" t="n">
+        <v>2595</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="B30" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>TMP2S2b2</t>
+          <t>TileMarkingPoint5S2b1</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>Tiles Point</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>196</v>
+        <v>-630</v>
       </c>
       <c r="F30" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>-150</v>
-      </c>
-      <c r="H30" t="n">
-        <v>1340</v>
+        <v>-775</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>blank</t>
+        </is>
       </c>
       <c r="I30" t="n">
-        <v>2595</v>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>blank</t>
-        </is>
+        <v>1940</v>
+      </c>
+      <c r="J30" t="n">
+        <v>2595</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B31" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>CP2S2</t>
+          <t>TileMarkingPoint5S2c1</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Tiles Point</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>-1230</v>
       </c>
       <c r="F31" t="n">
-        <v>966</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>975</v>
-      </c>
-      <c r="H31" t="n">
-        <v>1340</v>
+        <v>-775</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>blank</t>
+        </is>
       </c>
       <c r="I31" t="n">
-        <v>2595</v>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>blank</t>
-        </is>
+        <v>1940</v>
+      </c>
+      <c r="J31" t="n">
+        <v>2595</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="B32" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>TMP3S2a1</t>
+          <t>TileMarkingPoint6S2a1</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>Tiles Point</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>935</v>
+        <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>642</v>
+        <v>-296</v>
       </c>
       <c r="G32" t="n">
-        <v>-750</v>
-      </c>
-      <c r="H32" t="n">
-        <v>960</v>
+        <v>-775</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>blank</t>
+        </is>
       </c>
       <c r="I32" t="n">
-        <v>2595</v>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>blank</t>
-        </is>
+        <v>1932</v>
+      </c>
+      <c r="J32" t="n">
+        <v>2595</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="B33" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>TMP3S2a2</t>
+          <t>TileMarkingPoint6S2a2</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>Tiles Point</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>935</v>
+        <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>642</v>
+        <v>-296</v>
       </c>
       <c r="G33" t="n">
-        <v>-150</v>
-      </c>
-      <c r="H33" t="n">
-        <v>960</v>
+        <v>-175</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>blank</t>
+        </is>
       </c>
       <c r="I33" t="n">
-        <v>2595</v>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>blank</t>
-        </is>
+        <v>1932</v>
+      </c>
+      <c r="J33" t="n">
+        <v>2595</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="B34" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>TMP3S2a3</t>
+          <t>TileMarkingPoint6S2a3</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>Tiles Point</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>935</v>
+        <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>642</v>
+        <v>-296</v>
       </c>
       <c r="G34" t="n">
-        <v>450</v>
-      </c>
-      <c r="H34" t="n">
-        <v>960</v>
+        <v>425</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>blank</t>
+        </is>
       </c>
       <c r="I34" t="n">
-        <v>2595</v>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>blank</t>
-        </is>
+        <v>1932</v>
+      </c>
+      <c r="J34" t="n">
+        <v>2595</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="B35" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>TMP3S2a4</t>
+          <t>TileMarkingPoint6S2a4</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>Tiles Point</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>935</v>
+        <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>642</v>
+        <v>-296</v>
       </c>
       <c r="G35" t="n">
-        <v>1050</v>
-      </c>
-      <c r="H35" t="n">
-        <v>960</v>
+        <v>1025</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>blank</t>
+        </is>
       </c>
       <c r="I35" t="n">
-        <v>2595</v>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>blank</t>
-        </is>
+        <v>1932</v>
+      </c>
+      <c r="J35" t="n">
+        <v>2595</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="B36" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CP3S2</t>
+          <t>TileMarkingPoint6S2b1</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Tiles Point</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1450</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>304</v>
       </c>
       <c r="G36" t="n">
-        <v>975</v>
-      </c>
-      <c r="H36" t="n">
-        <v>960</v>
+        <v>-775</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>blank</t>
+        </is>
       </c>
       <c r="I36" t="n">
-        <v>2595</v>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>blank</t>
-        </is>
+        <v>1932</v>
+      </c>
+      <c r="J36" t="n">
+        <v>2595</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="B37" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>TMP4S2a1</t>
+          <t>TileMarkingPoint6S2b2</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>Tiles Point</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>-304</v>
+        <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>1940</v>
+        <v>304</v>
       </c>
       <c r="G37" t="n">
-        <v>-150</v>
-      </c>
-      <c r="H37" t="n">
-        <v>592</v>
+        <v>-175</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>blank</t>
+        </is>
       </c>
       <c r="I37" t="n">
-        <v>2595</v>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>blank</t>
-        </is>
+        <v>1932</v>
+      </c>
+      <c r="J37" t="n">
+        <v>2595</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="B38" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>TMP4S2a2</t>
+          <t>TileMarkingPoint6S2b3</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>Tiles Point</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>-304</v>
+        <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>1940</v>
+        <v>304</v>
       </c>
       <c r="G38" t="n">
-        <v>450</v>
-      </c>
-      <c r="H38" t="n">
-        <v>592</v>
+        <v>425</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>blank</t>
+        </is>
       </c>
       <c r="I38" t="n">
-        <v>2595</v>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>blank</t>
-        </is>
+        <v>1932</v>
+      </c>
+      <c r="J38" t="n">
+        <v>2595</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="B39" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>TMP4S2a3</t>
+          <t>TileMarkingPoint6S2b4</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>Tiles Point</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>-304</v>
+        <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>1940</v>
+        <v>304</v>
       </c>
       <c r="G39" t="n">
-        <v>1050</v>
-      </c>
-      <c r="H39" t="n">
-        <v>592</v>
+        <v>1025</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>blank</t>
+        </is>
       </c>
       <c r="I39" t="n">
-        <v>2595</v>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>blank</t>
-        </is>
+        <v>1932</v>
+      </c>
+      <c r="J39" t="n">
+        <v>2595</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>43</v>
-      </c>
-      <c r="B40" t="n">
-        <v>4</v>
+        <v>51</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>CP4S2</t>
+          <t>TileMarkingPoint7S2a1</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Tiles Point</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0</v>
+        <v>-1260</v>
       </c>
       <c r="F40" t="n">
-        <v>966</v>
+        <v>-746</v>
       </c>
       <c r="G40" t="n">
-        <v>975</v>
-      </c>
-      <c r="H40" t="n">
-        <v>592</v>
+        <v>-1050</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>blank</t>
+        </is>
       </c>
       <c r="I40" t="n">
-        <v>2595</v>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>blank</t>
-        </is>
+        <v>2900</v>
+      </c>
+      <c r="J40" t="n">
+        <v>1932</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>44</v>
-      </c>
-      <c r="B41" t="n">
-        <v>5</v>
+        <v>52</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>TMP5S2a1</t>
+          <t>TileMarkingPoint7S2a2</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>Tiles Point</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>-30</v>
+        <v>-1260</v>
       </c>
       <c r="F41" t="n">
-        <v>1340</v>
+        <v>-596</v>
       </c>
       <c r="G41" t="n">
-        <v>-750</v>
-      </c>
-      <c r="H41" t="n">
-        <v>1940</v>
+        <v>-1050</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>blank</t>
+        </is>
       </c>
       <c r="I41" t="n">
-        <v>2595</v>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>blank</t>
-        </is>
+        <v>2900</v>
+      </c>
+      <c r="J41" t="n">
+        <v>1932</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45</v>
-      </c>
-      <c r="B42" t="n">
-        <v>5</v>
+        <v>53</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>TMP5S2b1</t>
+          <t>TileMarkingPoint7S2a3</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>Tiles Point</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>-630</v>
+        <v>-1260</v>
       </c>
       <c r="F42" t="n">
-        <v>1340</v>
+        <v>-446</v>
       </c>
       <c r="G42" t="n">
-        <v>-750</v>
-      </c>
-      <c r="H42" t="n">
-        <v>1940</v>
+        <v>-1050</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>blank</t>
+        </is>
       </c>
       <c r="I42" t="n">
-        <v>2595</v>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>blank</t>
-        </is>
+        <v>2900</v>
+      </c>
+      <c r="J42" t="n">
+        <v>1932</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>46</v>
-      </c>
-      <c r="B43" t="n">
-        <v>5</v>
+        <v>54</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>TMP5S2c1</t>
+          <t>TileMarkingPoint7S2a4</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>Tiles Point</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>-1230</v>
+        <v>-1260</v>
       </c>
       <c r="F43" t="n">
-        <v>1340</v>
+        <v>-296</v>
       </c>
       <c r="G43" t="n">
-        <v>-750</v>
-      </c>
-      <c r="H43" t="n">
-        <v>1940</v>
+        <v>-1050</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>blank</t>
+        </is>
       </c>
       <c r="I43" t="n">
-        <v>2595</v>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>blank</t>
-        </is>
+        <v>2900</v>
+      </c>
+      <c r="J43" t="n">
+        <v>1932</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>48</v>
-      </c>
-      <c r="B44" t="n">
-        <v>5</v>
+        <v>55</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>CP5S2</t>
+          <t>TileMarkingPoint7S2a5</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Tiles Point</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1450</v>
+        <v>-1260</v>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>-146</v>
       </c>
       <c r="G44" t="n">
-        <v>975</v>
-      </c>
-      <c r="H44" t="n">
-        <v>1940</v>
+        <v>-1050</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>blank</t>
+        </is>
       </c>
       <c r="I44" t="n">
-        <v>2595</v>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>blank</t>
-        </is>
+        <v>2900</v>
+      </c>
+      <c r="J44" t="n">
+        <v>1932</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>49</v>
-      </c>
-      <c r="B45" t="n">
-        <v>6</v>
+        <v>56</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>TMP6S2a1</t>
+          <t>TileMarkingPoint7S2a6</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>Tiles Point</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>-296</v>
+        <v>-1260</v>
       </c>
       <c r="F45" t="n">
-        <v>1010</v>
+        <v>4</v>
       </c>
       <c r="G45" t="n">
-        <v>-750</v>
-      </c>
-      <c r="H45" t="n">
+        <v>-1050</v>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>blank</t>
+        </is>
+      </c>
+      <c r="I45" t="n">
+        <v>2900</v>
+      </c>
+      <c r="J45" t="n">
         <v>1932</v>
-      </c>
-      <c r="I45" t="n">
-        <v>2595</v>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>blank</t>
-        </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>50</v>
-      </c>
-      <c r="B46" t="n">
-        <v>6</v>
+        <v>57</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>TMP6S2a2</t>
+          <t>TileMarkingPoint7S2a7</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>Tiles Point</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>-296</v>
+        <v>-1260</v>
       </c>
       <c r="F46" t="n">
-        <v>1010</v>
+        <v>154</v>
       </c>
       <c r="G46" t="n">
-        <v>-150</v>
-      </c>
-      <c r="H46" t="n">
+        <v>-1050</v>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>blank</t>
+        </is>
+      </c>
+      <c r="I46" t="n">
+        <v>2900</v>
+      </c>
+      <c r="J46" t="n">
         <v>1932</v>
-      </c>
-      <c r="I46" t="n">
-        <v>2595</v>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>blank</t>
-        </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>51</v>
-      </c>
-      <c r="B47" t="n">
-        <v>6</v>
+        <v>58</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>TMP6S2a3</t>
+          <t>TileMarkingPoint7S2b1</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>Tiles Point</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>-296</v>
+        <v>-660</v>
       </c>
       <c r="F47" t="n">
-        <v>1010</v>
+        <v>-746</v>
       </c>
       <c r="G47" t="n">
-        <v>450</v>
-      </c>
-      <c r="H47" t="n">
+        <v>-1050</v>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>blank</t>
+        </is>
+      </c>
+      <c r="I47" t="n">
+        <v>2900</v>
+      </c>
+      <c r="J47" t="n">
         <v>1932</v>
-      </c>
-      <c r="I47" t="n">
-        <v>2595</v>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>blank</t>
-        </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>52</v>
-      </c>
-      <c r="B48" t="n">
-        <v>6</v>
+        <v>59</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>TMP6S2a4</t>
+          <t>TileMarkingPoint7S2b2</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>Tiles Point</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>-296</v>
+        <v>-660</v>
       </c>
       <c r="F48" t="n">
-        <v>1010</v>
+        <v>-596</v>
       </c>
       <c r="G48" t="n">
-        <v>1050</v>
-      </c>
-      <c r="H48" t="n">
+        <v>-1050</v>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>blank</t>
+        </is>
+      </c>
+      <c r="I48" t="n">
+        <v>2900</v>
+      </c>
+      <c r="J48" t="n">
         <v>1932</v>
-      </c>
-      <c r="I48" t="n">
-        <v>2595</v>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>blank</t>
-        </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>53</v>
-      </c>
-      <c r="B49" t="n">
-        <v>6</v>
+        <v>60</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>TMP6S2b1</t>
+          <t>TileMarkingPoint7S2b3</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>Tiles Point</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>304</v>
+        <v>-660</v>
       </c>
       <c r="F49" t="n">
-        <v>1010</v>
+        <v>-446</v>
       </c>
       <c r="G49" t="n">
-        <v>-750</v>
-      </c>
-      <c r="H49" t="n">
+        <v>-1050</v>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>blank</t>
+        </is>
+      </c>
+      <c r="I49" t="n">
+        <v>2900</v>
+      </c>
+      <c r="J49" t="n">
         <v>1932</v>
-      </c>
-      <c r="I49" t="n">
-        <v>2595</v>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>blank</t>
-        </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>54</v>
-      </c>
-      <c r="B50" t="n">
-        <v>6</v>
+        <v>61</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>TMP6S2b2</t>
+          <t>TileMarkingPoint7S2b4</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>Tiles Point</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>304</v>
+        <v>-660</v>
       </c>
       <c r="F50" t="n">
-        <v>1010</v>
+        <v>-296</v>
       </c>
       <c r="G50" t="n">
-        <v>-150</v>
-      </c>
-      <c r="H50" t="n">
+        <v>-1050</v>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>blank</t>
+        </is>
+      </c>
+      <c r="I50" t="n">
+        <v>2900</v>
+      </c>
+      <c r="J50" t="n">
         <v>1932</v>
-      </c>
-      <c r="I50" t="n">
-        <v>2595</v>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>blank</t>
-        </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>55</v>
-      </c>
-      <c r="B51" t="n">
-        <v>6</v>
+        <v>62</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>TMP6S2b3</t>
+          <t>TileMarkingPoint7S2b5</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>Tiles Point</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>304</v>
+        <v>-660</v>
       </c>
       <c r="F51" t="n">
-        <v>1010</v>
+        <v>-146</v>
       </c>
       <c r="G51" t="n">
-        <v>450</v>
-      </c>
-      <c r="H51" t="n">
+        <v>-1050</v>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>blank</t>
+        </is>
+      </c>
+      <c r="I51" t="n">
+        <v>2900</v>
+      </c>
+      <c r="J51" t="n">
         <v>1932</v>
-      </c>
-      <c r="I51" t="n">
-        <v>2595</v>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>blank</t>
-        </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>56</v>
-      </c>
-      <c r="B52" t="n">
-        <v>6</v>
+        <v>63</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>TMP6S2b4</t>
+          <t>TileMarkingPoint7S2b6</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>Tiles Point</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>304</v>
+        <v>-660</v>
       </c>
       <c r="F52" t="n">
-        <v>1010</v>
+        <v>4</v>
       </c>
       <c r="G52" t="n">
-        <v>1050</v>
-      </c>
-      <c r="H52" t="n">
+        <v>-1050</v>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>blank</t>
+        </is>
+      </c>
+      <c r="I52" t="n">
+        <v>2900</v>
+      </c>
+      <c r="J52" t="n">
         <v>1932</v>
-      </c>
-      <c r="I52" t="n">
-        <v>2595</v>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>blank</t>
-        </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>58</v>
-      </c>
-      <c r="B53" t="n">
-        <v>6</v>
+        <v>64</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>CP6S2</t>
+          <t>TileMarkingPoint7S2b7</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>Tiles Point</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>0</v>
+        <v>-660</v>
       </c>
       <c r="F53" t="n">
-        <v>966</v>
+        <v>154</v>
       </c>
       <c r="G53" t="n">
-        <v>975</v>
-      </c>
-      <c r="H53" t="n">
+        <v>-1050</v>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>blank</t>
+        </is>
+      </c>
+      <c r="I53" t="n">
+        <v>2900</v>
+      </c>
+      <c r="J53" t="n">
         <v>1932</v>
-      </c>
-      <c r="I53" t="n">
-        <v>2595</v>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>blank</t>
-        </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
@@ -2463,38 +2491,38 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>TMP7S2a1</t>
+          <t>TileMarkingPoint7S2c1</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>Tiles Point</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>-1260</v>
+        <v>30</v>
       </c>
       <c r="F54" t="n">
-        <v>-746</v>
+        <v>-296</v>
       </c>
       <c r="G54" t="n">
-        <v>-50</v>
-      </c>
-      <c r="H54" t="n">
-        <v>2900</v>
+        <v>-1025</v>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>blank</t>
+        </is>
       </c>
       <c r="I54" t="n">
+        <v>2900</v>
+      </c>
+      <c r="J54" t="n">
         <v>1932</v>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>blank</t>
-        </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
@@ -2503,38 +2531,38 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>TMP7S2a2</t>
+          <t>TileMarkingPoint7S2c2</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>Tiles Point</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>-1260</v>
+        <v>30</v>
       </c>
       <c r="F55" t="n">
-        <v>-596</v>
+        <v>304</v>
       </c>
       <c r="G55" t="n">
-        <v>-50</v>
-      </c>
-      <c r="H55" t="n">
-        <v>2900</v>
+        <v>-1025</v>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>blank</t>
+        </is>
       </c>
       <c r="I55" t="n">
+        <v>2900</v>
+      </c>
+      <c r="J55" t="n">
         <v>1932</v>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>blank</t>
-        </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
@@ -2543,38 +2571,38 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>TMP7S2a3</t>
+          <t>TileMarkingPoint7S2d1</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>Tiles Point</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>-1260</v>
+        <v>630</v>
       </c>
       <c r="F56" t="n">
-        <v>-446</v>
+        <v>-296</v>
       </c>
       <c r="G56" t="n">
-        <v>-50</v>
-      </c>
-      <c r="H56" t="n">
-        <v>2900</v>
+        <v>-1025</v>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>blank</t>
+        </is>
       </c>
       <c r="I56" t="n">
+        <v>2900</v>
+      </c>
+      <c r="J56" t="n">
         <v>1932</v>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>blank</t>
-        </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
@@ -2583,38 +2611,38 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>TMP7S2a4</t>
+          <t>TileMarkingPoint7S2d2</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>Tiles Point</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>-1260</v>
+        <v>630</v>
       </c>
       <c r="F57" t="n">
-        <v>-296</v>
+        <v>304</v>
       </c>
       <c r="G57" t="n">
-        <v>-50</v>
-      </c>
-      <c r="H57" t="n">
-        <v>2900</v>
+        <v>-1025</v>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>blank</t>
+        </is>
       </c>
       <c r="I57" t="n">
+        <v>2900</v>
+      </c>
+      <c r="J57" t="n">
         <v>1932</v>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>blank</t>
-        </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
@@ -2623,38 +2651,38 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>TMP7S2a5</t>
+          <t>TileMarkingPoint7S2e1</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>Tiles Point</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>-1260</v>
+        <v>1230</v>
       </c>
       <c r="F58" t="n">
-        <v>-146</v>
+        <v>-296</v>
       </c>
       <c r="G58" t="n">
-        <v>-50</v>
-      </c>
-      <c r="H58" t="n">
-        <v>2900</v>
+        <v>-1025</v>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>blank</t>
+        </is>
       </c>
       <c r="I58" t="n">
+        <v>2900</v>
+      </c>
+      <c r="J58" t="n">
         <v>1932</v>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>blank</t>
-        </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
@@ -2663,633 +2691,33 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>TMP7S2a6</t>
+          <t>TileMarkingPoint7S2e2</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>Tiles Point</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>-1260</v>
+        <v>1230</v>
       </c>
       <c r="F59" t="n">
-        <v>4</v>
+        <v>304</v>
       </c>
       <c r="G59" t="n">
-        <v>-50</v>
-      </c>
-      <c r="H59" t="n">
-        <v>2900</v>
+        <v>-1025</v>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>blank</t>
+        </is>
       </c>
       <c r="I59" t="n">
+        <v>2900</v>
+      </c>
+      <c r="J59" t="n">
         <v>1932</v>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>blank</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="1" t="n">
-        <v>65</v>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>TMP7S2a7</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="E60" t="n">
-        <v>-1260</v>
-      </c>
-      <c r="F60" t="n">
-        <v>154</v>
-      </c>
-      <c r="G60" t="n">
-        <v>-50</v>
-      </c>
-      <c r="H60" t="n">
-        <v>2900</v>
-      </c>
-      <c r="I60" t="n">
-        <v>1932</v>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>blank</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="1" t="n">
-        <v>66</v>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>TMP7S2b1</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="E61" t="n">
-        <v>-660</v>
-      </c>
-      <c r="F61" t="n">
-        <v>-746</v>
-      </c>
-      <c r="G61" t="n">
-        <v>-50</v>
-      </c>
-      <c r="H61" t="n">
-        <v>2900</v>
-      </c>
-      <c r="I61" t="n">
-        <v>1932</v>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>blank</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="1" t="n">
-        <v>67</v>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>TMP7S2b2</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="E62" t="n">
-        <v>-660</v>
-      </c>
-      <c r="F62" t="n">
-        <v>-596</v>
-      </c>
-      <c r="G62" t="n">
-        <v>-50</v>
-      </c>
-      <c r="H62" t="n">
-        <v>2900</v>
-      </c>
-      <c r="I62" t="n">
-        <v>1932</v>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>blank</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="1" t="n">
-        <v>68</v>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>TMP7S2b3</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="E63" t="n">
-        <v>-660</v>
-      </c>
-      <c r="F63" t="n">
-        <v>-446</v>
-      </c>
-      <c r="G63" t="n">
-        <v>-50</v>
-      </c>
-      <c r="H63" t="n">
-        <v>2900</v>
-      </c>
-      <c r="I63" t="n">
-        <v>1932</v>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>blank</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="1" t="n">
-        <v>69</v>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>TMP7S2b4</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="E64" t="n">
-        <v>-660</v>
-      </c>
-      <c r="F64" t="n">
-        <v>-296</v>
-      </c>
-      <c r="G64" t="n">
-        <v>-50</v>
-      </c>
-      <c r="H64" t="n">
-        <v>2900</v>
-      </c>
-      <c r="I64" t="n">
-        <v>1932</v>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>blank</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="1" t="n">
-        <v>70</v>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>TMP7S2b5</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="E65" t="n">
-        <v>-660</v>
-      </c>
-      <c r="F65" t="n">
-        <v>-146</v>
-      </c>
-      <c r="G65" t="n">
-        <v>-50</v>
-      </c>
-      <c r="H65" t="n">
-        <v>2900</v>
-      </c>
-      <c r="I65" t="n">
-        <v>1932</v>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>blank</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="1" t="n">
-        <v>71</v>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>TMP7S2b6</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="E66" t="n">
-        <v>-660</v>
-      </c>
-      <c r="F66" t="n">
-        <v>4</v>
-      </c>
-      <c r="G66" t="n">
-        <v>-50</v>
-      </c>
-      <c r="H66" t="n">
-        <v>2900</v>
-      </c>
-      <c r="I66" t="n">
-        <v>1932</v>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>blank</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="1" t="n">
-        <v>72</v>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>TMP7S2b7</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="E67" t="n">
-        <v>-660</v>
-      </c>
-      <c r="F67" t="n">
-        <v>154</v>
-      </c>
-      <c r="G67" t="n">
-        <v>-50</v>
-      </c>
-      <c r="H67" t="n">
-        <v>2900</v>
-      </c>
-      <c r="I67" t="n">
-        <v>1932</v>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>blank</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="1" t="n">
-        <v>73</v>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>TMP7S2c1</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="E68" t="n">
-        <v>30</v>
-      </c>
-      <c r="F68" t="n">
-        <v>-296</v>
-      </c>
-      <c r="G68" t="n">
-        <v>-25</v>
-      </c>
-      <c r="H68" t="n">
-        <v>2900</v>
-      </c>
-      <c r="I68" t="n">
-        <v>1932</v>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>blank</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="1" t="n">
-        <v>74</v>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>TMP7S2c2</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="E69" t="n">
-        <v>30</v>
-      </c>
-      <c r="F69" t="n">
-        <v>304</v>
-      </c>
-      <c r="G69" t="n">
-        <v>-25</v>
-      </c>
-      <c r="H69" t="n">
-        <v>2900</v>
-      </c>
-      <c r="I69" t="n">
-        <v>1932</v>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>blank</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="1" t="n">
-        <v>75</v>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>TMP7S2d1</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="E70" t="n">
-        <v>630</v>
-      </c>
-      <c r="F70" t="n">
-        <v>-296</v>
-      </c>
-      <c r="G70" t="n">
-        <v>-25</v>
-      </c>
-      <c r="H70" t="n">
-        <v>2900</v>
-      </c>
-      <c r="I70" t="n">
-        <v>1932</v>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>blank</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="1" t="n">
-        <v>76</v>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>TMP7S2d2</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="E71" t="n">
-        <v>630</v>
-      </c>
-      <c r="F71" t="n">
-        <v>304</v>
-      </c>
-      <c r="G71" t="n">
-        <v>-25</v>
-      </c>
-      <c r="H71" t="n">
-        <v>2900</v>
-      </c>
-      <c r="I71" t="n">
-        <v>1932</v>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>blank</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="1" t="n">
-        <v>77</v>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>TMP7S2e1</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="E72" t="n">
-        <v>1230</v>
-      </c>
-      <c r="F72" t="n">
-        <v>-296</v>
-      </c>
-      <c r="G72" t="n">
-        <v>-25</v>
-      </c>
-      <c r="H72" t="n">
-        <v>2900</v>
-      </c>
-      <c r="I72" t="n">
-        <v>1932</v>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>blank</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="1" t="n">
-        <v>78</v>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>TMP7S2e2</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="E73" t="n">
-        <v>1230</v>
-      </c>
-      <c r="F73" t="n">
-        <v>304</v>
-      </c>
-      <c r="G73" t="n">
-        <v>-25</v>
-      </c>
-      <c r="H73" t="n">
-        <v>2900</v>
-      </c>
-      <c r="I73" t="n">
-        <v>1932</v>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>blank</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="1" t="n">
-        <v>85</v>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>CP7S2</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>?</t>
-        </is>
-      </c>
-      <c r="E74" t="n">
-        <v>1450</v>
-      </c>
-      <c r="F74" t="n">
-        <v>966</v>
-      </c>
-      <c r="G74" t="n">
-        <v>-25</v>
-      </c>
-      <c r="H74" t="n">
-        <v>2900</v>
-      </c>
-      <c r="I74" t="n">
-        <v>1932</v>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>blank</t>
-        </is>
       </c>
     </row>
   </sheetData>
@@ -3303,7 +2731,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3355,32 +2783,32 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Shower Ledge2:Shower Ledge:1090921</t>
+          <t>BSS.GOMGO.TR.GG-6108-600:Chrome 000:1090991</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Fitting</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>-1450</v>
+        <v>-60</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="G2" t="n">
-        <v>-162</v>
+        <v>175</v>
       </c>
       <c r="H2" t="n">
-        <v>2760</v>
+        <v>2900</v>
       </c>
       <c r="I2" t="n">
         <v>2595</v>
@@ -3393,32 +2821,32 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>BSS.GOMGO.TR.GG-6108-600:Chrome 000:1090991</t>
+          <t>BSS.GESSI.SM.49079:29046000:1090989</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>Fitting</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>-60</v>
+        <v>725</v>
       </c>
       <c r="F3" t="n">
-        <v>70</v>
+        <v>1270</v>
       </c>
       <c r="G3" t="n">
-        <v>200</v>
+        <v>-50</v>
       </c>
       <c r="H3" t="n">
-        <v>2760</v>
+        <v>960</v>
       </c>
       <c r="I3" t="n">
         <v>2595</v>
@@ -3431,29 +2859,29 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B4" t="n">
         <v>3</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>BSS.GESSI.SM.49079:29046000:1090989</t>
+          <t>BSS.HAND SHOWER SET.MASTER BATH:BSS.HAND SHOWER SET.MASTER BATH:1091130</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>Fitting</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>725</v>
+        <v>912</v>
       </c>
       <c r="F4" t="n">
-        <v>-662</v>
+        <v>1270</v>
       </c>
       <c r="G4" t="n">
-        <v>-25</v>
+        <v>962</v>
       </c>
       <c r="H4" t="n">
         <v>960</v>
@@ -3469,32 +2897,32 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="B5" t="n">
         <v>4</v>
       </c>
-      <c r="B5" t="n">
-        <v>3</v>
-      </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>BSS.HAND SHOWER SET.MASTER BATH:BSS.HAND SHOWER SET.MASTER BATH:1091130</t>
+          <t>BSS.GOMGO.PH.GG-6106:Chrome 000:1090992</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Fitting</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>912</v>
+        <v>-434</v>
       </c>
       <c r="F5" t="n">
-        <v>-662</v>
+        <v>1030</v>
       </c>
       <c r="G5" t="n">
-        <v>987</v>
+        <v>-375</v>
       </c>
       <c r="H5" t="n">
-        <v>960</v>
+        <v>592</v>
       </c>
       <c r="I5" t="n">
         <v>2595</v>
@@ -3507,32 +2935,32 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="B6" t="n">
         <v>5</v>
       </c>
-      <c r="B6" t="n">
-        <v>4</v>
-      </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>BSS.GOMGO.PH.GG-6106:Chrome 000:1090992</t>
+          <t>BSS.TECE.CHAIR BRACKET.9370228:BSS.TECE.CHAIR BRACKET.9370228:1090922</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>Fitting</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>-434</v>
+        <v>-30</v>
       </c>
       <c r="F6" t="n">
-        <v>-902</v>
+        <v>1687</v>
       </c>
       <c r="G6" t="n">
-        <v>-350</v>
+        <v>-786</v>
       </c>
       <c r="H6" t="n">
-        <v>600</v>
+        <v>1940</v>
       </c>
       <c r="I6" t="n">
         <v>2595</v>
@@ -3545,32 +2973,32 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B7" t="n">
         <v>5</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BSS.TECE.CHAIR BRACKET.9370228:BSS.TECE.CHAIR BRACKET.9370228:1090922</t>
+          <t>BSS.BASIN CABINET.C5-MASTER BATH:BSS.BASIN CABINET.C5-MASTER BATH:1090928</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Fitting</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>-30</v>
+        <v>-930</v>
       </c>
       <c r="F7" t="n">
-        <v>-245</v>
+        <v>1870</v>
       </c>
       <c r="G7" t="n">
-        <v>-761</v>
+        <v>-275</v>
       </c>
       <c r="H7" t="n">
-        <v>1800</v>
+        <v>1940</v>
       </c>
       <c r="I7" t="n">
         <v>2595</v>
@@ -3583,32 +3011,32 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B8" t="n">
         <v>5</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BSS.BASIN CABINET.C5-MASTER BATH:BSS.BASIN CABINET.C5-MASTER BATH:1090928</t>
+          <t>BSS.TECE.CONCEALED CISTERN.9370224:BSS.TECE.CONCEALED CISTERN.9370224:1090923</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Fitting</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>-930</v>
+        <v>-25</v>
       </c>
       <c r="F8" t="n">
-        <v>-62</v>
+        <v>1782</v>
       </c>
       <c r="G8" t="n">
-        <v>-250</v>
+        <v>-156</v>
       </c>
       <c r="H8" t="n">
-        <v>1800</v>
+        <v>1940</v>
       </c>
       <c r="I8" t="n">
         <v>2595</v>
@@ -3621,32 +3049,32 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B9" t="n">
         <v>5</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BSS.TECE.CONCEALED CISTERN.9370224:BSS.TECE.CONCEALED CISTERN.9370224:1090923</t>
+          <t>BSS.MIRROR CABINET.C5-MASTER BATH:BSS.MIRROR CABINET.C5-MASTER BATH:1090945</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Fitting</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>-25</v>
+        <v>-480</v>
       </c>
       <c r="F9" t="n">
-        <v>-150</v>
+        <v>1870</v>
       </c>
       <c r="G9" t="n">
-        <v>-131</v>
+        <v>125</v>
       </c>
       <c r="H9" t="n">
-        <v>1800</v>
+        <v>1940</v>
       </c>
       <c r="I9" t="n">
         <v>2595</v>
@@ -3659,35 +3087,37 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" t="n">
-        <v>5</v>
+        <v>10</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BSS.MIRROR CABINET.C5-MASTER BATH:BSS.MIRROR CABINET.C5-MASTER BATH:1090945</t>
+          <t>BSS.FLOOR DRAIN_100:BSS.FLOOR DRAIN_100:1091045</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Fitting</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>-480</v>
+        <v>-370</v>
       </c>
       <c r="F10" t="n">
-        <v>-62</v>
+        <v>639</v>
       </c>
       <c r="G10" t="n">
-        <v>150</v>
+        <v>-1025</v>
       </c>
       <c r="H10" t="n">
-        <v>1800</v>
+        <v>2900</v>
       </c>
       <c r="I10" t="n">
-        <v>2595</v>
+        <v>1932</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -3697,7 +3127,7 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -3706,70 +3136,30 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BSS.FLOOR DRAIN_100:BSS.FLOOR DRAIN_100:1091045</t>
+          <t>BSS.FLOOR DRAIN_150:BSS.FLOOR DRAIN_150:1091065</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Fitting</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>-370</v>
+        <v>-735</v>
       </c>
       <c r="F11" t="n">
-        <v>639</v>
+        <v>179</v>
       </c>
       <c r="G11" t="n">
-        <v>-25</v>
+        <v>-1050</v>
       </c>
       <c r="H11" t="n">
-        <v>1800</v>
+        <v>2900</v>
       </c>
       <c r="I11" t="n">
-        <v>2595</v>
+        <v>1932</v>
       </c>
       <c r="J11" t="inlineStr">
-        <is>
-          <t>blank</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>BSS.FLOOR DRAIN_150:BSS.FLOOR DRAIN_150:1091065</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>-735</v>
-      </c>
-      <c r="F12" t="n">
-        <v>179</v>
-      </c>
-      <c r="G12" t="n">
-        <v>-50</v>
-      </c>
-      <c r="H12" t="n">
-        <v>1800</v>
-      </c>
-      <c r="I12" t="n">
-        <v>2595</v>
-      </c>
-      <c r="J12" t="inlineStr">
         <is>
           <t>blank</t>
         </is>
